--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7829028B-EE04-4D06-BD91-30EF1B40E59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E77E6-0CE6-4707-A7B5-D1C31993F333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
@@ -7992,44 +7992,44 @@
         <v>22</v>
       </c>
       <c r="F114" s="23">
-        <v>0</v>
+        <v>202552.53</v>
       </c>
       <c r="G114" s="23">
-        <v>0</v>
+        <v>23299.85</v>
       </c>
       <c r="H114" s="23">
-        <v>0</v>
+        <v>35551.699999999997</v>
       </c>
       <c r="I114" s="23">
         <v>0</v>
       </c>
       <c r="J114" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>261404.08000000002</v>
       </c>
       <c r="K114" s="23">
-        <v>0</v>
-      </c>
-      <c r="L114" s="25" t="str">
+        <v>2318.4899999999998</v>
+      </c>
+      <c r="L114" s="25">
         <f t="shared" si="10"/>
-        <v/>
+        <v>8.7913977176849126E-3</v>
       </c>
       <c r="M114" s="24">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>263722.57</v>
       </c>
       <c r="N114" s="68">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-0.35129109451047125</v>
       </c>
       <c r="O114" s="23">
-        <v>0</v>
+        <v>1079.48</v>
       </c>
       <c r="P114" s="66">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="Q114" s="62">
-        <v>0</v>
+        <v>0.17169999999999999</v>
       </c>
       <c r="R114" s="48"/>
       <c r="S114" s="48"/>
@@ -8167,15 +8167,15 @@
       <c r="S116" s="48"/>
       <c r="T116" s="51">
         <f>AVERAGEIF(O110:O121,"&gt;1")</f>
-        <v>1285.1724999999999</v>
+        <v>1244.0340000000001</v>
       </c>
       <c r="U116" s="72">
         <f>(T116-T104)/T104</f>
-        <v>3.7957073919276309E-2</v>
+        <v>4.7319643830639052E-3</v>
       </c>
       <c r="W116" s="44">
         <f>AVERAGEIF(Q110:Q121,"&gt;1%")</f>
-        <v>0.56817499999999999</v>
+        <v>0.48887999999999998</v>
       </c>
       <c r="X116" s="5"/>
     </row>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="N121" s="61">
-        <f t="shared" ref="N121:N122" si="15">IF(M121=0,0,(M121-M109)/M109)</f>
+        <f t="shared" ref="N121" si="15">IF(M121=0,0,(M121-M109)/M109)</f>
         <v>0</v>
       </c>
       <c r="O121" s="63">
@@ -8484,11 +8484,11 @@
       <c r="S121" s="53"/>
       <c r="T121" s="43">
         <f>SUM(M110:M121)</f>
-        <v>3653285.1</v>
+        <v>3917007.67</v>
       </c>
       <c r="U121" s="60">
         <f>(T121-T109)/T109</f>
-        <v>-0.54646625881543753</v>
+        <v>-0.51372666129349542</v>
       </c>
       <c r="V121" s="45">
         <f>V109+1</f>

--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E77E6-0CE6-4707-A7B5-D1C31993F333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1E7D6-0C0B-4A8A-A79D-0E266683CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
+    <workbookView xWindow="3510" yWindow="1455" windowWidth="15615" windowHeight="14745" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
   <sheets>
     <sheet name="DATABASE TOT" sheetId="1" r:id="rId1"/>
@@ -513,7 +513,18 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Percent 2" xfId="2" xr:uid="{14F17EFC-A1E3-4093-969F-1B5CA78DE294}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7957,7 +7968,7 @@
         <f t="shared" si="11"/>
         <v>441418.37</v>
       </c>
-      <c r="N113" s="49">
+      <c r="N113" s="68">
         <f t="shared" si="6"/>
         <v>-0.22801147161490598</v>
       </c>
@@ -8053,44 +8064,44 @@
         <v>23</v>
       </c>
       <c r="F115" s="23">
-        <v>0</v>
+        <v>256921.66</v>
       </c>
       <c r="G115" s="23">
-        <v>0</v>
+        <v>32169.96</v>
       </c>
       <c r="H115" s="23">
-        <v>0</v>
+        <v>16380</v>
       </c>
       <c r="I115" s="23">
         <v>0</v>
       </c>
       <c r="J115" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>305471.62</v>
       </c>
       <c r="K115" s="23">
-        <v>0</v>
-      </c>
-      <c r="L115" s="25" t="str">
+        <v>3070</v>
+      </c>
+      <c r="L115" s="25">
         <f t="shared" si="10"/>
-        <v/>
+        <v>9.9500352659067526E-3</v>
       </c>
       <c r="M115" s="24">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N115" s="49">
+        <v>308541.62</v>
+      </c>
+      <c r="N115" s="68">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-0.21169379960597162</v>
       </c>
       <c r="O115" s="23">
-        <v>0</v>
+        <v>1052.96</v>
       </c>
       <c r="P115" s="66">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="Q115" s="62">
-        <v>0</v>
+        <v>0.23730000000000001</v>
       </c>
       <c r="R115" s="48"/>
       <c r="S115" s="48"/>
@@ -8167,15 +8178,15 @@
       <c r="S116" s="48"/>
       <c r="T116" s="51">
         <f>AVERAGEIF(O110:O121,"&gt;1")</f>
-        <v>1244.0340000000001</v>
+        <v>1212.1883333333333</v>
       </c>
       <c r="U116" s="72">
         <f>(T116-T104)/T104</f>
-        <v>4.7319643830639052E-3</v>
+        <v>-2.0987878665509059E-2</v>
       </c>
       <c r="W116" s="44">
         <f>AVERAGEIF(Q110:Q121,"&gt;1%")</f>
-        <v>0.48887999999999998</v>
+        <v>0.44694999999999996</v>
       </c>
       <c r="X116" s="5"/>
     </row>
@@ -8484,11 +8495,11 @@
       <c r="S121" s="53"/>
       <c r="T121" s="43">
         <f>SUM(M110:M121)</f>
-        <v>3917007.67</v>
+        <v>4225549.29</v>
       </c>
       <c r="U121" s="60">
         <f>(T121-T109)/T109</f>
-        <v>-0.51372666129349542</v>
+        <v>-0.47542304375492839</v>
       </c>
       <c r="V121" s="45">
         <f>V109+1</f>
@@ -8498,6 +8509,14 @@
       <c r="X121" s="55"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N1:N1048576">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1E7D6-0C0B-4A8A-A79D-0E266683CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F1DD0E-4D44-41B1-B117-B2503D9DA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1455" windowWidth="15615" windowHeight="14745" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
   <sheets>
     <sheet name="DATABASE TOT" sheetId="1" r:id="rId1"/>
@@ -516,12 +516,12 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
       </font>
     </dxf>
   </dxfs>
@@ -8134,25 +8134,15 @@
       <c r="E116" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F116" s="23">
-        <v>0</v>
-      </c>
-      <c r="G116" s="23">
-        <v>0</v>
-      </c>
-      <c r="H116" s="23">
-        <v>0</v>
-      </c>
-      <c r="I116" s="23">
-        <v>0</v>
-      </c>
+      <c r="F116" s="23"/>
+      <c r="G116" s="23"/>
+      <c r="H116" s="23"/>
+      <c r="I116" s="23"/>
       <c r="J116" s="24">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K116" s="23">
-        <v>0</v>
-      </c>
+      <c r="K116" s="23"/>
       <c r="L116" s="25" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8165,15 +8155,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O116" s="23">
-        <v>0</v>
-      </c>
-      <c r="P116" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="62">
-        <v>0</v>
-      </c>
+      <c r="O116" s="23"/>
+      <c r="P116" s="66"/>
+      <c r="Q116" s="62"/>
       <c r="R116" s="48"/>
       <c r="S116" s="48"/>
       <c r="T116" s="51">
@@ -8207,25 +8191,15 @@
       <c r="E117" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="F117" s="23">
-        <v>0</v>
-      </c>
-      <c r="G117" s="23">
-        <v>0</v>
-      </c>
-      <c r="H117" s="23">
-        <v>0</v>
-      </c>
-      <c r="I117" s="23">
-        <v>0</v>
-      </c>
+      <c r="F117" s="23"/>
+      <c r="G117" s="23"/>
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
       <c r="J117" s="24">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K117" s="23">
-        <v>0</v>
-      </c>
+      <c r="K117" s="23"/>
       <c r="L117" s="25" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8238,15 +8212,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O117" s="23">
-        <v>0</v>
-      </c>
-      <c r="P117" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="62">
-        <v>0</v>
-      </c>
+      <c r="O117" s="23"/>
+      <c r="P117" s="66"/>
+      <c r="Q117" s="62"/>
       <c r="R117" s="48"/>
       <c r="S117" s="48"/>
       <c r="X117" s="5"/>
@@ -8268,25 +8236,15 @@
       <c r="E118" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F118" s="23">
-        <v>0</v>
-      </c>
-      <c r="G118" s="23">
-        <v>0</v>
-      </c>
-      <c r="H118" s="23">
-        <v>0</v>
-      </c>
-      <c r="I118" s="23">
-        <v>0</v>
-      </c>
+      <c r="F118" s="23"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
       <c r="J118" s="24">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K118" s="23">
-        <v>0</v>
-      </c>
+      <c r="K118" s="23"/>
       <c r="L118" s="25" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8299,15 +8257,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O118" s="23">
-        <v>0</v>
-      </c>
-      <c r="P118" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="62">
-        <v>0</v>
-      </c>
+      <c r="O118" s="23"/>
+      <c r="P118" s="66"/>
+      <c r="Q118" s="62"/>
       <c r="R118" s="48"/>
       <c r="S118" s="48"/>
       <c r="X118" s="5"/>
@@ -8329,25 +8281,15 @@
       <c r="E119" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F119" s="23">
-        <v>0</v>
-      </c>
-      <c r="G119" s="23">
-        <v>0</v>
-      </c>
-      <c r="H119" s="23">
-        <v>0</v>
-      </c>
-      <c r="I119" s="23">
-        <v>0</v>
-      </c>
+      <c r="F119" s="23"/>
+      <c r="G119" s="23"/>
+      <c r="H119" s="23"/>
+      <c r="I119" s="23"/>
       <c r="J119" s="24">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K119" s="23">
-        <v>0</v>
-      </c>
+      <c r="K119" s="23"/>
       <c r="L119" s="25" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8360,15 +8302,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O119" s="23">
-        <v>0</v>
-      </c>
-      <c r="P119" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="62">
-        <v>0</v>
-      </c>
+      <c r="O119" s="23"/>
+      <c r="P119" s="66"/>
+      <c r="Q119" s="62"/>
       <c r="R119" s="48"/>
       <c r="S119" s="48"/>
       <c r="X119" s="5"/>
@@ -8390,25 +8326,15 @@
       <c r="E120" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F120" s="23">
-        <v>0</v>
-      </c>
-      <c r="G120" s="23">
-        <v>0</v>
-      </c>
-      <c r="H120" s="23">
-        <v>0</v>
-      </c>
-      <c r="I120" s="23">
-        <v>0</v>
-      </c>
+      <c r="F120" s="23"/>
+      <c r="G120" s="23"/>
+      <c r="H120" s="23"/>
+      <c r="I120" s="23"/>
       <c r="J120" s="24">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K120" s="23">
-        <v>0</v>
-      </c>
+      <c r="K120" s="23"/>
       <c r="L120" s="25" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8421,15 +8347,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O120" s="23">
-        <v>0</v>
-      </c>
-      <c r="P120" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q120" s="62">
-        <v>0</v>
-      </c>
+      <c r="O120" s="23"/>
+      <c r="P120" s="66"/>
+      <c r="Q120" s="62"/>
       <c r="R120" s="48"/>
       <c r="S120" s="48"/>
       <c r="X120" s="5"/>
@@ -8451,25 +8371,15 @@
       <c r="E121" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F121" s="63">
-        <v>0</v>
-      </c>
-      <c r="G121" s="63">
-        <v>0</v>
-      </c>
-      <c r="H121" s="63">
-        <v>0</v>
-      </c>
-      <c r="I121" s="63">
-        <v>0</v>
-      </c>
+      <c r="F121" s="63"/>
+      <c r="G121" s="63"/>
+      <c r="H121" s="63"/>
+      <c r="I121" s="63"/>
       <c r="J121" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K121" s="63">
-        <v>0</v>
-      </c>
+      <c r="K121" s="63"/>
       <c r="L121" s="37" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -8482,15 +8392,9 @@
         <f t="shared" ref="N121" si="15">IF(M121=0,0,(M121-M109)/M109)</f>
         <v>0</v>
       </c>
-      <c r="O121" s="63">
-        <v>0</v>
-      </c>
-      <c r="P121" s="71">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="64">
-        <v>0</v>
-      </c>
+      <c r="O121" s="63"/>
+      <c r="P121" s="71"/>
+      <c r="Q121" s="64"/>
       <c r="R121" s="52"/>
       <c r="S121" s="53"/>
       <c r="T121" s="43">
@@ -8510,10 +8414,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_BRASIL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Desktop\Documents\GitHub\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F1DD0E-4D44-41B1-B117-B2503D9DA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C83D9B-39DB-4AAE-81F7-F74AAB5D274A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
   <sheets>
     <sheet name="DATABASE TOT" sheetId="1" r:id="rId1"/>
@@ -8134,43 +8134,59 @@
       <c r="E116" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
-      <c r="H116" s="23"/>
-      <c r="I116" s="23"/>
+      <c r="F116" s="23">
+        <v>530465.11</v>
+      </c>
+      <c r="G116" s="23">
+        <v>76662.2</v>
+      </c>
+      <c r="H116" s="23">
+        <v>33325</v>
+      </c>
+      <c r="I116" s="23">
+        <v>0</v>
+      </c>
       <c r="J116" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K116" s="23"/>
-      <c r="L116" s="25" t="str">
+        <v>640452.30999999994</v>
+      </c>
+      <c r="K116" s="23">
+        <v>7728.72</v>
+      </c>
+      <c r="L116" s="25">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1.1923705943692924E-2</v>
       </c>
       <c r="M116" s="24">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>648181.02999999991</v>
       </c>
       <c r="N116" s="49">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="23"/>
-      <c r="P116" s="66"/>
-      <c r="Q116" s="62"/>
+        <v>0.19647329084085979</v>
+      </c>
+      <c r="O116" s="23">
+        <v>1116.27</v>
+      </c>
+      <c r="P116" s="66">
+        <v>473</v>
+      </c>
+      <c r="Q116" s="62">
+        <v>0.44879999999999998</v>
+      </c>
       <c r="R116" s="48"/>
       <c r="S116" s="48"/>
       <c r="T116" s="51">
         <f>AVERAGEIF(O110:O121,"&gt;1")</f>
-        <v>1212.1883333333333</v>
+        <v>1198.4857142857143</v>
       </c>
       <c r="U116" s="72">
         <f>(T116-T104)/T104</f>
-        <v>-2.0987878665509059E-2</v>
+        <v>-3.2054665709036034E-2</v>
       </c>
       <c r="W116" s="44">
         <f>AVERAGEIF(Q110:Q121,"&gt;1%")</f>
-        <v>0.44694999999999996</v>
+        <v>0.44721428571428568</v>
       </c>
       <c r="X116" s="5"/>
     </row>
@@ -8399,11 +8415,11 @@
       <c r="S121" s="53"/>
       <c r="T121" s="43">
         <f>SUM(M110:M121)</f>
-        <v>4225549.29</v>
+        <v>4873730.32</v>
       </c>
       <c r="U121" s="60">
         <f>(T121-T109)/T109</f>
-        <v>-0.47542304375492839</v>
+        <v>-0.39495520194845041</v>
       </c>
       <c r="V121" s="45">
         <f>V109+1</f>

--- a/DB Arcoiris Dashboard.xlsx
+++ b/DB Arcoiris Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Desktop\Documents\GitHub\DASHBOARD_BRASIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C83D9B-39DB-4AAE-81F7-F74AAB5D274A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D575E8-B28E-4C49-B01C-49F8C050805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4DC6B9C3-1844-4AFD-84C5-8F1E979BB903}"/>
   </bookViews>
@@ -8178,15 +8178,15 @@
       <c r="S116" s="48"/>
       <c r="T116" s="51">
         <f>AVERAGEIF(O110:O121,"&gt;1")</f>
-        <v>1198.4857142857143</v>
+        <v>1180.2987499999999</v>
       </c>
       <c r="U116" s="72">
         <f>(T116-T104)/T104</f>
-        <v>-3.2054665709036034E-2</v>
+        <v>-4.6743190582914394E-2</v>
       </c>
       <c r="W116" s="44">
         <f>AVERAGEIF(Q110:Q121,"&gt;1%")</f>
-        <v>0.44721428571428568</v>
+        <v>0.45463749999999997</v>
       </c>
       <c r="X116" s="5"/>
     </row>
@@ -8207,30 +8207,46 @@
       <c r="E117" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
+      <c r="F117" s="23">
+        <v>566507.80000000005</v>
+      </c>
+      <c r="G117" s="23">
+        <v>82005.069999999949</v>
+      </c>
+      <c r="H117" s="23">
+        <v>53240</v>
+      </c>
+      <c r="I117" s="23">
+        <v>0</v>
+      </c>
       <c r="J117" s="24">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K117" s="23"/>
-      <c r="L117" s="25" t="str">
+        <v>701752.87</v>
+      </c>
+      <c r="K117" s="23">
+        <v>8000.88</v>
+      </c>
+      <c r="L117" s="25">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1.1272754811087648E-2</v>
       </c>
       <c r="M117" s="24">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>709753.75</v>
       </c>
       <c r="N117" s="49">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O117" s="23"/>
-      <c r="P117" s="66"/>
-      <c r="Q117" s="62"/>
+        <v>0.42922865596470205</v>
+      </c>
+      <c r="O117" s="23">
+        <v>1052.99</v>
+      </c>
+      <c r="P117" s="66">
+        <v>534</v>
+      </c>
+      <c r="Q117" s="62">
+        <v>0.50660000000000005</v>
+      </c>
       <c r="R117" s="48"/>
       <c r="S117" s="48"/>
       <c r="X117" s="5"/>
@@ -8415,11 +8431,11 @@
       <c r="S121" s="53"/>
       <c r="T121" s="43">
         <f>SUM(M110:M121)</f>
-        <v>4873730.32</v>
+        <v>5583484.0700000003</v>
       </c>
       <c r="U121" s="60">
         <f>(T121-T109)/T109</f>
-        <v>-0.39495520194845041</v>
+        <v>-0.30684347106895438</v>
       </c>
       <c r="V121" s="45">
         <f>V109+1</f>
